--- a/data/export/2026-10-07-operations.xlsx
+++ b/data/export/2026-10-07-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -442,7 +442,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:13</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,33 +704,37 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -759,32 +767,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -792,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,33 +828,37 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -875,32 +891,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -908,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -932,33 +952,37 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1048,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1063,7 +1087,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1074,7 +1098,7 @@
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1164,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1190,7 +1214,7 @@
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1280,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1330,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1396,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1446,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1512,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1538,7 +1562,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1628,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1654,35 +1678,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1739,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:44</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1758,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1794,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1831,12 +1855,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1874,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1875,46 +1899,50 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1975,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +1994,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,46 +2019,50 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2095,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2114,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2107,46 +2139,50 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2215,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2234,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2270,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2331,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2350,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,7 +2375,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2350,7 +2386,7 @@
       <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -2363,22 +2399,22 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2416,7 +2452,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2466,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2466,7 +2502,7 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2515,7 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2489,7 +2525,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2527,12 +2563,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2582,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,35 +2618,35 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2643,12 +2679,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2662,7 +2698,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2698,35 +2734,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2759,12 +2795,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2778,7 +2814,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2814,35 +2850,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2875,12 +2911,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2894,7 +2930,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2930,7 +2966,2939 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>76分钟</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>3/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>2/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>3/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-07-operations.xlsx
+++ b/data/export/2026-10-07-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD46"/>
+  <dimension ref="A1:AD66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1015,32 +1015,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1048,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1072,17 +1076,17 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1092,13 +1096,17 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1131,32 +1139,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1164,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1188,33 +1200,37 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1247,32 +1263,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1280,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1304,33 +1324,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1363,32 +1387,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1396,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1420,33 +1448,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1479,32 +1511,36 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1512,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1536,33 +1572,37 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1595,32 +1635,36 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1628,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1652,33 +1696,37 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1711,32 +1759,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:44</t>
@@ -1744,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1768,33 +1820,37 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1827,32 +1883,36 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1860,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1884,17 +1944,17 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1904,17 +1964,17 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1980,7 +2040,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2034,7 +2094,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2160,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2139,7 +2199,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2154,7 +2214,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2280,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2336,7 +2396,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2380,41 +2440,45 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2447,12 +2511,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2466,7 +2530,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2491,46 +2555,50 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2563,12 +2631,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2582,7 +2650,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2607,46 +2675,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2679,12 +2751,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2698,7 +2770,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2723,46 +2795,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2795,12 +2871,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2814,7 +2890,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2839,46 +2915,50 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2911,12 +2991,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:44</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2930,7 +3010,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2955,46 +3035,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3027,12 +3111,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3046,7 +3130,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3071,46 +3155,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3143,12 +3231,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3162,7 +3250,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3187,18 +3275,22 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3303,7 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3221,7 +3313,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3231,40 +3323,44 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3278,7 +3374,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3288,33 +3384,37 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>3/25</t>
         </is>
       </c>
     </row>
@@ -3327,7 +3427,7 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3337,7 +3437,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3347,40 +3447,44 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3394,7 +3498,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3404,33 +3508,37 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>4/25</t>
         </is>
       </c>
     </row>
@@ -3443,60 +3551,64 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:43</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3510,7 +3622,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3520,17 +3632,17 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3540,13 +3652,17 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3675,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3569,7 +3685,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3579,40 +3695,44 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:43</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3626,7 +3746,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3636,17 +3756,17 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3656,13 +3776,17 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3799,7 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3685,7 +3809,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3695,40 +3819,44 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3742,7 +3870,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3752,17 +3880,17 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3772,13 +3900,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>5/25</t>
         </is>
       </c>
     </row>
@@ -3791,7 +3923,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3801,7 +3933,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3839,12 +3971,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:43</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3858,7 +3990,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3894,7 +4026,7 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -3907,7 +4039,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3917,7 +4049,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3955,12 +4087,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3974,7 +4106,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4010,7 +4142,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4155,7 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4033,7 +4165,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4071,12 +4203,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4090,7 +4222,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4126,7 +4258,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4139,22 +4271,22 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4187,12 +4319,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4206,7 +4338,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4242,7 +4374,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4387,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4265,7 +4397,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4303,12 +4435,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:43</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4322,7 +4454,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4358,7 +4490,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4371,7 +4503,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4381,7 +4513,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4419,12 +4551,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:43</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4438,7 +4570,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4474,7 +4606,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4487,7 +4619,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4497,7 +4629,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4535,12 +4667,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4554,7 +4686,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4590,77 +4722,73 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:43</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4674,7 +4802,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4684,107 +4812,99 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr">
-        <is>
-          <t>76.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4798,7 +4918,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4808,65 +4928,61 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4899,12 +5015,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4918,7 +5034,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4954,77 +5070,73 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5038,7 +5150,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5048,17 +5160,17 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5068,45 +5180,41 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5139,12 +5247,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5158,7 +5266,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5194,35 +5302,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A53893D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5255,12 +5363,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5274,7 +5382,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5310,35 +5418,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5371,12 +5479,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5390,7 +5498,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5426,35 +5534,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5487,12 +5595,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5506,7 +5614,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5531,50 +5639,46 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC43" s="2" t="inlineStr">
-        <is>
-          <t>76.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5607,12 +5711,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5626,7 +5730,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5662,35 +5766,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5723,12 +5827,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:43</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5742,7 +5846,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5778,35 +5882,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5839,12 +5943,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5858,47 +5962,2427 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>3/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>4/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>07:34</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>76分钟</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>76分钟</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
           <t>08:15</t>
         </is>
       </c>
-      <c r="W46" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X46" s="2" t="inlineStr">
+      <c r="X61" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y46" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z46" s="2" t="inlineStr">
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
+      <c r="AA61" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB46" s="2" t="inlineStr">
+      <c r="AB61" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC46" s="2" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="AD46" s="2" t="inlineStr">
-        <is>
-          <t>1/9</t>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-07-operations.xlsx
+++ b/data/export/2026-10-07-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD66"/>
+  <dimension ref="A1:AD95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,22 +843,22 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,22 +1091,22 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1215,22 +1215,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1339,22 +1339,22 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1463,22 +1463,22 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1592,17 +1592,17 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1893,12 +1893,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2007,32 +2007,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2040,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2064,37 +2068,37 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2127,32 +2131,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2160,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2184,17 +2192,17 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2204,7 +2212,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2214,7 +2222,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2247,32 +2255,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -2280,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2304,33 +2316,37 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2363,32 +2379,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2396,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2420,37 +2440,37 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2483,32 +2503,36 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2516,7 +2540,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2540,37 +2564,37 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2603,32 +2627,36 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -2636,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2660,37 +2688,37 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2723,32 +2751,36 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2756,7 +2788,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2780,17 +2812,17 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2800,17 +2832,17 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -2843,32 +2875,36 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2876,7 +2912,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2900,37 +2936,37 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2996,7 +3032,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3035,7 +3071,7 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -3050,7 +3086,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3152,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3155,7 +3191,7 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
@@ -3183,22 +3219,22 @@
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A68870D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3236,7 +3272,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3250,7 +3286,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3280,87 +3316,83 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3374,7 +3406,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3384,17 +3416,17 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3409,82 +3441,78 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>3/25</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3498,7 +3526,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3508,107 +3536,103 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>4/25</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3622,7 +3646,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3632,107 +3656,103 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3746,7 +3766,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3756,107 +3776,103 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3870,7 +3886,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3880,65 +3896,65 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>5/25</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3976,7 +3992,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3990,7 +4006,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4015,46 +4031,50 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -4087,12 +4107,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4106,7 +4126,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4131,46 +4151,50 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4203,12 +4227,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:44</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4222,7 +4246,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4247,18 +4271,22 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -4271,60 +4299,64 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4338,7 +4370,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4348,33 +4380,37 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -4387,7 +4423,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4397,7 +4433,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4407,40 +4443,44 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:43</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4454,7 +4494,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4464,33 +4504,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4547,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4513,7 +4557,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4523,40 +4567,44 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:43</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4570,7 +4618,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4580,33 +4628,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -4619,60 +4671,64 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4686,7 +4742,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4696,33 +4752,37 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -4735,60 +4795,64 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:43</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4802,7 +4866,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4812,33 +4876,37 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -4851,60 +4919,64 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4918,7 +4990,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4928,33 +5000,37 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -4967,60 +5043,64 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5034,7 +5114,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5044,33 +5124,37 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5167,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5093,7 +5177,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5103,40 +5187,44 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5150,7 +5238,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5160,33 +5248,37 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -5199,7 +5291,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5209,7 +5301,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5219,40 +5311,44 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5266,7 +5362,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5276,33 +5372,37 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -5315,60 +5415,64 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:43</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5382,7 +5486,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5392,33 +5496,37 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -5431,60 +5539,64 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:43</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5498,7 +5610,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5508,17 +5620,17 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5528,13 +5640,17 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5663,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5557,7 +5673,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5567,40 +5683,44 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5614,7 +5734,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5624,33 +5744,37 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5787,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5673,7 +5797,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5711,12 +5835,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:43</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5730,7 +5854,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5766,7 +5890,7 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -5779,7 +5903,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5789,7 +5913,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5827,12 +5951,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:43</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5846,7 +5970,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5882,7 +6006,7 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -5895,7 +6019,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5905,7 +6029,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5943,12 +6067,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5962,7 +6086,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5998,7 +6122,7 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6011,22 +6135,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>08:28</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6064,7 +6188,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6078,7 +6202,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6114,7 +6238,7 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6127,22 +6251,22 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6175,12 +6299,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6194,7 +6318,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6230,7 +6354,7 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6243,22 +6367,22 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A53893D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>08:38</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6291,12 +6415,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6310,7 +6434,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6335,22 +6459,18 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC49" s="2" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>3/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6363,22 +6483,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6411,12 +6531,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6430,7 +6550,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6455,92 +6575,84 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC50" s="2" t="inlineStr">
-        <is>
-          <t>129.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>4/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr"/>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6554,7 +6666,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6564,107 +6676,99 @@
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC51" s="2" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6678,7 +6782,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6688,107 +6792,99 @@
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:43</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6802,7 +6898,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6812,107 +6908,99 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6926,7 +7014,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6936,65 +7024,61 @@
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>76.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -7027,12 +7111,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7046,7 +7130,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7071,7 +7155,7 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
@@ -7082,77 +7166,73 @@
       <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7166,7 +7246,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7176,17 +7256,17 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7196,45 +7276,41 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>76.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7267,12 +7343,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7286,7 +7362,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7311,46 +7387,50 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB57" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -7383,12 +7463,12 @@
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7402,7 +7482,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7437,40 +7517,40 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7503,12 +7583,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7522,7 +7602,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7558,35 +7638,35 @@
       <c r="AC59" s="2" t="inlineStr"/>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7619,12 +7699,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7638,7 +7718,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7663,46 +7743,50 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB60" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7735,12 +7819,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7754,7 +7838,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7789,40 +7873,40 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7855,12 +7939,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7874,7 +7958,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7909,40 +7993,40 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7975,12 +8059,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7994,7 +8078,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -8029,40 +8113,40 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8095,12 +8179,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8114,7 +8198,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8139,46 +8223,50 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB64" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8211,12 +8299,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8230,7 +8318,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8260,41 +8348,45 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8327,12 +8419,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8346,7 +8438,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8382,7 +8474,3515 @@
       <c r="AC66" s="2" t="inlineStr"/>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>9/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>9/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>07:34</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>76分钟</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>77分钟</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-07-operations.xlsx
+++ b/data/export/2026-10-07-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>9/12</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>8/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>7/12</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1964,17 +1964,17 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>9/12</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2336,17 +2336,17 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>7/12</t>
+          <t>9/12</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>8/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>7/12</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3444,17 +3444,17 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>7/12</t>
+          <t>9/12</t>
         </is>
       </c>
     </row>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>7/12</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>8/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4312,12 +4312,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4560,17 +4560,17 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>7/12</t>
+          <t>9/12</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>8/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5428,17 +5428,17 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>7/12</t>
+          <t>9/12</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5800,17 +5800,17 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>9/12</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6301,12 +6301,12 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>8/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6668,17 +6668,17 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>9/12</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AD51" s="2" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -7120,7 +7120,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7169,12 +7169,12 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>8/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7288,17 +7288,17 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>7/12</t>
+          <t>9/12</t>
         </is>
       </c>
     </row>
@@ -7616,7 +7616,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>7/12</t>
         </is>
       </c>
     </row>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>7/12</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7904,17 +7904,17 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>9/12</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8400,17 +8400,17 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>7/12</t>
+          <t>9/12</t>
         </is>
       </c>
     </row>
@@ -8728,7 +8728,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>7/12</t>
         </is>
       </c>
     </row>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -9020,17 +9020,17 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>9/12</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -9149,12 +9149,12 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>8/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -9348,7 +9348,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9640,17 +9640,17 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>7/12</t>
+          <t>9/12</t>
         </is>
       </c>
     </row>
@@ -9817,12 +9817,12 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>20:37</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>67分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9893,12 +9893,12 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>7/12</t>
         </is>
       </c>
     </row>
@@ -9941,24 +9941,24 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:47</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>8/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -10055,32 +10055,36 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10088,7 +10092,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10112,17 +10116,17 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -10132,17 +10136,17 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>9/12</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
@@ -10175,32 +10179,36 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
           <t>06:44</t>
@@ -10208,7 +10216,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10232,17 +10240,17 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -10252,12 +10260,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
@@ -10295,32 +10303,36 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -10328,7 +10340,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10352,17 +10364,17 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -10372,17 +10384,17 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>7/12</t>
+          <t>9/12</t>
         </is>
       </c>
     </row>
@@ -10448,7 +10460,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10497,12 +10509,12 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>7/12</t>
         </is>
       </c>
     </row>
@@ -10568,7 +10580,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10612,17 +10624,17 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>9/12</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
@@ -10746,7 +10758,7 @@
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -10870,7 +10882,7 @@
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10952,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -11312,7 +11324,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11490,7 +11502,7 @@
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -11738,7 +11750,7 @@
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -11808,7 +11820,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11852,17 +11864,17 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -11932,7 +11944,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -12056,7 +12068,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12100,12 +12112,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
@@ -12420,7 +12432,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12664,7 +12676,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12708,17 +12720,17 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>126.2</t>
         </is>
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -12842,7 +12854,7 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -12912,7 +12924,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -12966,7 +12978,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -13036,7 +13048,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -13085,12 +13097,12 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AD102" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -13160,7 +13172,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13209,7 +13221,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>128.2</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AD103" s="2" t="inlineStr">
@@ -13284,7 +13296,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -13462,7 +13474,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -13532,7 +13544,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -13576,17 +13588,17 @@
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -13826,7 +13838,7 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -13950,7 +13962,7 @@
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -14020,7 +14032,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -14144,7 +14156,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14446,7 +14458,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -14640,7 +14652,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14814,7 +14826,7 @@
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -15012,7 +15024,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15056,17 +15068,17 @@
       </c>
       <c r="AB118" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC118" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -15260,7 +15272,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15304,12 +15316,12 @@
       </c>
       <c r="AB120" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC120" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AD120" s="2" t="inlineStr">
@@ -15384,7 +15396,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15756,7 +15768,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15880,7 +15892,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -15924,17 +15936,17 @@
       </c>
       <c r="AB125" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC125" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>126.2</t>
         </is>
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -16128,7 +16140,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -16182,7 +16194,7 @@
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -16252,7 +16264,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -16301,7 +16313,7 @@
       </c>
       <c r="AC128" s="2" t="inlineStr">
         <is>
-          <t>128.2</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AD128" s="2" t="inlineStr">
@@ -16376,7 +16388,7 @@
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
@@ -16678,7 +16690,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16760,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -17174,7 +17186,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -17748,7 +17760,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -18120,7 +18132,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18174,7 +18186,7 @@
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -18244,7 +18256,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18293,7 +18305,7 @@
       </c>
       <c r="AC144" s="2" t="inlineStr">
         <is>
-          <t>128.2</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AD144" s="2" t="inlineStr">
@@ -18422,7 +18434,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -18670,7 +18682,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -18918,7 +18930,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -19042,7 +19054,7 @@
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -19166,7 +19178,7 @@
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -19492,7 +19504,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -19536,17 +19548,17 @@
       </c>
       <c r="AB154" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC154" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -19612,7 +19624,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -19661,12 +19673,12 @@
       </c>
       <c r="AC155" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -19732,7 +19744,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19776,12 +19788,12 @@
       </c>
       <c r="AB156" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC156" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AD156" s="2" t="inlineStr">
@@ -19856,7 +19868,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19900,17 +19912,17 @@
       </c>
       <c r="AB157" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC157" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -19980,7 +19992,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -20104,7 +20116,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20148,17 +20160,17 @@
       </c>
       <c r="AB159" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC159" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>126.2</t>
         </is>
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -20228,7 +20240,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20352,7 +20364,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
@@ -20476,7 +20488,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -20600,7 +20612,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q163" s="2" t="inlineStr">
@@ -20844,7 +20856,7 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q165" s="2" t="inlineStr">
@@ -21022,7 +21034,7 @@
       </c>
       <c r="AD166" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -21212,7 +21224,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -21514,7 +21526,7 @@
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -21638,7 +21650,7 @@
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -22177,24 +22189,24 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="inlineStr"/>
       <c r="M176" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N176" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O176" s="2" t="inlineStr">
@@ -22204,7 +22216,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22253,7 +22265,7 @@
       </c>
       <c r="AC176" s="2" t="inlineStr">
         <is>
-          <t>128.2</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AD176" s="2" t="inlineStr">
@@ -22291,32 +22303,36 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="2" t="inlineStr"/>
       <c r="M177" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N177" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
           <t>06:43</t>
@@ -22324,7 +22340,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22348,17 +22364,17 @@
       </c>
       <c r="X177" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z177" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA177" s="2" t="inlineStr">
@@ -22368,17 +22384,17 @@
       </c>
       <c r="AB177" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC177" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -22421,12 +22437,12 @@
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>20:54</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr"/>
@@ -22448,7 +22464,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22497,12 +22513,12 @@
       </c>
       <c r="AC178" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -22535,12 +22551,12 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq63，推进35站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
@@ -22568,7 +22584,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22576,10 +22592,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R179" s="2" t="inlineStr"/>
-      <c r="S179" s="2" t="inlineStr"/>
-      <c r="T179" s="2" t="inlineStr"/>
-      <c r="U179" s="2" t="inlineStr"/>
+      <c r="R179" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S179" s="2" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
+      <c r="T179" s="2" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="U179" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="V179" s="2" t="inlineStr">
         <is>
           <t>19:00</t>
@@ -22655,32 +22687,36 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="2" t="inlineStr"/>
       <c r="M180" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N180" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -22688,7 +22724,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22712,17 +22748,17 @@
       </c>
       <c r="X180" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z180" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA180" s="2" t="inlineStr">
@@ -22732,12 +22768,12 @@
       </c>
       <c r="AB180" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC180" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AD180" s="2" t="inlineStr">
@@ -22775,32 +22811,36 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="2" t="inlineStr"/>
       <c r="M181" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N181" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O181" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -22808,7 +22848,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -22832,17 +22872,17 @@
       </c>
       <c r="X181" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z181" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA181" s="2" t="inlineStr">
@@ -22852,17 +22892,17 @@
       </c>
       <c r="AB181" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC181" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -22895,12 +22935,12 @@
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq54，推进26站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
@@ -22928,7 +22968,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -22936,10 +22976,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R182" s="2" t="inlineStr"/>
-      <c r="S182" s="2" t="inlineStr"/>
-      <c r="T182" s="2" t="inlineStr"/>
-      <c r="U182" s="2" t="inlineStr"/>
+      <c r="R182" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S182" s="2" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="T182" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="U182" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V182" s="2" t="inlineStr">
         <is>
           <t>19:20</t>
@@ -23048,7 +23104,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23135,32 +23191,36 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:38</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="K184" s="2" t="inlineStr"/>
       <c r="L184" s="2" t="inlineStr"/>
       <c r="M184" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N184" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N184" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -23168,7 +23228,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23192,17 +23252,17 @@
       </c>
       <c r="X184" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z184" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA184" s="2" t="inlineStr">
@@ -23212,17 +23272,17 @@
       </c>
       <c r="AB184" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC184" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>126.2</t>
         </is>
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -23288,7 +23348,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23408,7 +23468,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23462,7 +23522,7 @@
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -23528,7 +23588,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q187" s="2" t="inlineStr">
@@ -23648,7 +23708,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -23768,7 +23828,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -24884,7 +24944,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -25008,7 +25068,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25057,12 +25117,12 @@
       </c>
       <c r="AC199" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD199" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -25504,7 +25564,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25548,12 +25608,12 @@
       </c>
       <c r="AB203" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC203" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD203" s="2" t="inlineStr">
@@ -26000,7 +26060,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q207" s="2" t="inlineStr">
@@ -26044,12 +26104,12 @@
       </c>
       <c r="AB207" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC207" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AD207" s="2" t="inlineStr">
@@ -26124,7 +26184,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q208" s="2" t="inlineStr">
@@ -26168,17 +26228,17 @@
       </c>
       <c r="AB208" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC208" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD208" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -26248,7 +26308,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q209" s="2" t="inlineStr">
@@ -26292,17 +26352,17 @@
       </c>
       <c r="AB209" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC209" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -26616,7 +26676,7 @@
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q212" s="2" t="inlineStr">
@@ -26860,7 +26920,7 @@
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q214" s="2" t="inlineStr">
@@ -26909,12 +26969,12 @@
       </c>
       <c r="AC214" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD214" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -27356,7 +27416,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q218" s="2" t="inlineStr">
@@ -27400,12 +27460,12 @@
       </c>
       <c r="AB218" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC218" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD218" s="2" t="inlineStr">
@@ -27604,7 +27664,7 @@
       </c>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q220" s="2" t="inlineStr">
@@ -27648,12 +27708,12 @@
       </c>
       <c r="AB220" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC220" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AD220" s="2" t="inlineStr">
@@ -27724,7 +27784,7 @@
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q221" s="2" t="inlineStr">
@@ -27768,17 +27828,17 @@
       </c>
       <c r="AB221" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC221" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -27972,7 +28032,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q223" s="2" t="inlineStr">
@@ -28016,17 +28076,17 @@
       </c>
       <c r="AB223" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC223" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD223" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -28096,7 +28156,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q224" s="2" t="inlineStr">
@@ -28145,12 +28205,12 @@
       </c>
       <c r="AC224" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD224" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -28468,7 +28528,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q227" s="2" t="inlineStr">
@@ -28512,12 +28572,12 @@
       </c>
       <c r="AB227" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC227" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD227" s="2" t="inlineStr">
@@ -28716,7 +28776,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
@@ -28760,12 +28820,12 @@
       </c>
       <c r="AB229" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC229" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AD229" s="2" t="inlineStr">
@@ -28964,7 +29024,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q231" s="2" t="inlineStr">
@@ -29008,17 +29068,17 @@
       </c>
       <c r="AB231" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC231" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD231" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -29088,7 +29148,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q232" s="2" t="inlineStr">
@@ -29132,17 +29192,17 @@
       </c>
       <c r="AB232" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC232" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD232" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -29336,7 +29396,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q234" s="2" t="inlineStr">
@@ -29380,17 +29440,17 @@
       </c>
       <c r="AB234" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC234" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AD234" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -29956,7 +30016,7 @@
       </c>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q239" s="2" t="inlineStr">
@@ -30000,17 +30060,17 @@
       </c>
       <c r="AB239" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC239" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD239" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -30080,7 +30140,7 @@
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q240" s="2" t="inlineStr">
@@ -30204,7 +30264,7 @@
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q241" s="2" t="inlineStr">
@@ -30248,17 +30308,17 @@
       </c>
       <c r="AB241" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC241" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AD241" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -30328,7 +30388,7 @@
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q242" s="2" t="inlineStr">
@@ -30377,12 +30437,12 @@
       </c>
       <c r="AC242" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD242" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -30824,7 +30884,7 @@
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q246" s="2" t="inlineStr">
@@ -30868,12 +30928,12 @@
       </c>
       <c r="AB246" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC246" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD246" s="2" t="inlineStr">
@@ -31072,7 +31132,7 @@
       </c>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q248" s="2" t="inlineStr">
@@ -31116,12 +31176,12 @@
       </c>
       <c r="AB248" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC248" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AD248" s="2" t="inlineStr">
@@ -31196,7 +31256,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q249" s="2" t="inlineStr">
@@ -31564,7 +31624,7 @@
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q252" s="2" t="inlineStr">
@@ -31613,12 +31673,12 @@
       </c>
       <c r="AC252" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD252" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -31688,7 +31748,7 @@
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q253" s="2" t="inlineStr">
@@ -31732,17 +31792,17 @@
       </c>
       <c r="AB253" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC253" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD253" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -31812,7 +31872,7 @@
       </c>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q254" s="2" t="inlineStr">
@@ -31856,17 +31916,17 @@
       </c>
       <c r="AB254" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC254" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD254" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -32060,7 +32120,7 @@
       </c>
       <c r="P256" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q256" s="2" t="inlineStr">
@@ -32104,17 +32164,17 @@
       </c>
       <c r="AB256" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC256" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AD256" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -32552,7 +32612,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q260" s="2" t="inlineStr">
@@ -32596,12 +32656,12 @@
       </c>
       <c r="AB260" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC260" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD260" s="2" t="inlineStr">
@@ -32800,7 +32860,7 @@
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q262" s="2" t="inlineStr">
@@ -32844,12 +32904,12 @@
       </c>
       <c r="AB262" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC262" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AD262" s="2" t="inlineStr">
@@ -33296,7 +33356,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q266" s="2" t="inlineStr">
@@ -33416,7 +33476,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -33460,17 +33520,17 @@
       </c>
       <c r="AB267" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC267" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -33536,7 +33596,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -33580,17 +33640,17 @@
       </c>
       <c r="AB268" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC268" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD268" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -33660,7 +33720,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -33709,12 +33769,12 @@
       </c>
       <c r="AC269" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD269" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -33784,7 +33844,7 @@
       </c>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q270" s="2" t="inlineStr">
@@ -33828,17 +33888,17 @@
       </c>
       <c r="AB270" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC270" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AD270" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -34400,7 +34460,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q275" s="2" t="inlineStr">
@@ -34444,12 +34504,12 @@
       </c>
       <c r="AB275" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC275" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD275" s="2" t="inlineStr">
@@ -34644,7 +34704,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q277" s="2" t="inlineStr">
@@ -34688,12 +34748,12 @@
       </c>
       <c r="AB277" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC277" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AD277" s="2" t="inlineStr">
@@ -35125,12 +35185,12 @@
       <c r="L281" s="2" t="inlineStr"/>
       <c r="M281" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N281" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O281" s="2" t="inlineStr">
@@ -35140,7 +35200,7 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
@@ -35227,32 +35287,36 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="J282" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K282" s="2" t="inlineStr"/>
       <c r="L282" s="2" t="inlineStr"/>
       <c r="M282" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N282" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N282" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O282" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -35260,7 +35324,7 @@
       </c>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q282" s="2" t="inlineStr">
@@ -35284,17 +35348,17 @@
       </c>
       <c r="X282" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y282" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z282" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA282" s="2" t="inlineStr">
@@ -35304,17 +35368,17 @@
       </c>
       <c r="AB282" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC282" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD282" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -35597,24 +35661,24 @@
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K285" s="2" t="inlineStr"/>
       <c r="L285" s="2" t="inlineStr"/>
       <c r="M285" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N285" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O285" s="2" t="inlineStr">
@@ -35624,7 +35688,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35673,12 +35737,12 @@
       </c>
       <c r="AC285" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD285" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -35711,32 +35775,36 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K286" s="2" t="inlineStr"/>
       <c r="L286" s="2" t="inlineStr"/>
       <c r="M286" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N286" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N286" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O286" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -35744,7 +35812,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35768,17 +35836,17 @@
       </c>
       <c r="X286" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z286" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA286" s="2" t="inlineStr">
@@ -35788,17 +35856,17 @@
       </c>
       <c r="AB286" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC286" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD286" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -35831,32 +35899,36 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="2" t="inlineStr"/>
       <c r="M287" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N287" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N287" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O287" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -35864,7 +35936,7 @@
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q287" s="2" t="inlineStr">
@@ -35888,17 +35960,17 @@
       </c>
       <c r="X287" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z287" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA287" s="2" t="inlineStr">
@@ -35908,17 +35980,17 @@
       </c>
       <c r="AB287" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC287" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AD287" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -35951,32 +36023,36 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="2" t="inlineStr"/>
       <c r="M288" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N288" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N288" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O288" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -35984,7 +36060,7 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
@@ -36008,17 +36084,17 @@
       </c>
       <c r="X288" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y288" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z288" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA288" s="2" t="inlineStr">
@@ -36028,12 +36104,12 @@
       </c>
       <c r="AB288" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC288" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD288" s="2" t="inlineStr">
@@ -36071,32 +36147,36 @@
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:58</t>
         </is>
       </c>
       <c r="J289" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K289" s="2" t="inlineStr"/>
       <c r="L289" s="2" t="inlineStr"/>
       <c r="M289" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N289" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N289" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O289" s="2" t="inlineStr">
         <is>
           <t>08:30</t>
@@ -36104,7 +36184,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -36128,17 +36208,17 @@
       </c>
       <c r="X289" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y289" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z289" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA289" s="2" t="inlineStr">
@@ -36148,12 +36228,12 @@
       </c>
       <c r="AB289" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC289" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AD289" s="2" t="inlineStr">
@@ -36224,7 +36304,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q290" s="2" t="inlineStr">
@@ -36268,17 +36348,17 @@
       </c>
       <c r="AB290" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC290" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD290" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -36344,7 +36424,7 @@
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q291" s="2" t="inlineStr">
@@ -36388,17 +36468,17 @@
       </c>
       <c r="AB291" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC291" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AD291" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
